--- a/Products_import.xlsx
+++ b/Products_import.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IMG_001.png</t>
+          <t>IMG_001.jpg</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>IMG_002.png</t>
+          <t>IMG_002.jpg</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IMG_003.png</t>
+          <t>IMG_003.jpg</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IMG_004.png</t>
+          <t>IMG_004.jpg</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IMG_005.png</t>
+          <t>IMG_005.jpg</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IMG_006.png</t>
+          <t>IMG_006.jpg</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IMG_007.png</t>
+          <t>IMG_007.jpg</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IMG_008.png</t>
+          <t>IMG_008.jpg</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IMG_009.png</t>
+          <t>IMG_009.jpg</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>IMG_010.png</t>
+          <t>IMG_010.jpg</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>IMG_011.png</t>
+          <t>IMG_011.jpg</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IMG_012.png</t>
+          <t>IMG_012.jpg</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>IMG_013.png</t>
+          <t>IMG_013.jpg</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>IMG_014.png</t>
+          <t>IMG_014.jpg</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>IMG_015.png</t>
+          <t>IMG_015.jpg</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>IMG_016.png</t>
+          <t>IMG_016.jpg</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>IMG_017.png</t>
+          <t>IMG_017.jpg</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>IMG_018.png</t>
+          <t>IMG_018.jpg</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IMG_019.png</t>
+          <t>IMG_019.jpg</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IMG_020.png</t>
+          <t>IMG_020.jpg</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IMG_021.png</t>
+          <t>IMG_021.jpg</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>IMG_022.png</t>
+          <t>IMG_022.jpg</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>IMG_023.png</t>
+          <t>IMG_023.jpg</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IMG_024.png</t>
+          <t>IMG_024.jpg</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IMG_025.png</t>
+          <t>IMG_025.jpg</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>IMG_026.png</t>
+          <t>IMG_026.jpg</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>IMG_027.png</t>
+          <t>IMG_027.jpg</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>IMG_028.png</t>
+          <t>IMG_028.jpg</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>IMG_029.png</t>
+          <t>IMG_029.jpg</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>IMG_030.png</t>
+          <t>IMG_030.jpg</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>IMG_031.png</t>
+          <t>IMG_031.jpg</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salomon</t>
+          <t>Hoka</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>IMG_032.png</t>
+          <t>IMG_032.jpg</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IMG_033.png</t>
+          <t>IMG_033.jpg</t>
         </is>
       </c>
     </row>
